--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
@@ -914,10 +914,10 @@
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G16" s="15">
         <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>28.571428571428</v>
+        <v>100</v>
       </c>
       <c r="I16" s="15">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J16" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-9.090909090909</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M16" s="14">
-        <v>-41.176470588235</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.294117647058</v>
+        <v>-77.333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,37 +975,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>58.333333333333</v>
+        <v>76.923076923076</v>
       </c>
       <c r="I17" s="15">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J17" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K17" s="14">
-        <v>58.823529411764</v>
+        <v>63.636363636363</v>
       </c>
       <c r="L17" s="14">
         <v>200</v>
       </c>
       <c r="M17" s="14">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="N17" s="14">
         <v>50</v>
@@ -1015,23 +1015,23 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>0</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="15">
         <v>5</v>
@@ -1043,13 +1043,13 @@
         <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M18" s="14">
-        <v>-85.294117647058</v>
+        <v>-86.486486486486</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.75</v>
+        <v>-94.382022471910</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
         <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="F19" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G19" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H19" s="14">
-        <v>-6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J19" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K19" s="14">
-        <v>-9.523809523809</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L19" s="14">
-        <v>-51.282051282051</v>
+        <v>-43.181818181818</v>
       </c>
       <c r="M19" s="14">
-        <v>-29.629629629629</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>-52.5</v>
+        <v>-46.808510638297</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
         <v>3</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
       <c r="E20" s="14">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I20" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K20" s="14">
-        <v>-8.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="14">
-        <v>-47.619047619047</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M20" s="14">
-        <v>-38.888888888888</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.6</v>
+        <v>-95.890410958904</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>18.181818181818</v>
+        <v>37.5</v>
       </c>
       <c r="F21" s="17">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G21" s="17">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H21" s="18">
-        <v>18.75</v>
+        <v>24.074074074074</v>
       </c>
       <c r="I21" s="17">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="J21" s="17">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="K21" s="18">
-        <v>8.823529411764</v>
+        <v>15.476190476190</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.941176470588</v>
+        <v>-2.020202020202</v>
       </c>
       <c r="M21" s="18">
-        <v>-33.333333333333</v>
+        <v>-21.138211382113</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.842794759825</v>
+        <v>-81.663516068052</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="14">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G23" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H23" s="14">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J23" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K23" s="14">
         <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M23" s="14">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14">
-        <v>15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="F24" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G24" s="15">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H24" s="14">
         <v>0</v>
       </c>
       <c r="I24" s="15">
+        <v>69</v>
+      </c>
+      <c r="J24" s="15">
         <v>57</v>
       </c>
-      <c r="J24" s="15">
-        <v>46</v>
-      </c>
       <c r="K24" s="14">
-        <v>23.913043478260</v>
+        <v>21.052631578947</v>
       </c>
       <c r="L24" s="14">
-        <v>-8.064516129032</v>
+        <v>0</v>
       </c>
       <c r="M24" s="14">
-        <v>32.558139534883</v>
+        <v>40.816326530612</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="14">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="14">
-        <v>85.714285714285</v>
+        <v>75</v>
       </c>
       <c r="I25" s="15">
+        <v>18</v>
+      </c>
+      <c r="J25" s="15">
         <v>17</v>
       </c>
-      <c r="J25" s="15">
-        <v>14</v>
-      </c>
       <c r="K25" s="14">
-        <v>21.428571428571</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L25" s="14">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
         <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F26" s="15">
         <v>32</v>
       </c>
       <c r="G26" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H26" s="14">
-        <v>52.380952380952</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I26" s="15">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J26" s="15">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K26" s="14">
-        <v>31.25</v>
+        <v>35.135135135135</v>
       </c>
       <c r="L26" s="14">
-        <v>13.513513513513</v>
+        <v>16.279069767441</v>
       </c>
       <c r="M26" s="14">
-        <v>-6.666666666666</v>
+        <v>6.382978723404</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
@@ -1406,10 +1406,10 @@
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -905,19 +905,19 @@
         <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>7</v>
-      </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14">
-        <v>250</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
         <v>14</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="I16" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15">
         <v>12</v>
       </c>
       <c r="K16" s="14">
-        <v>41.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L16" s="14">
-        <v>21.428571428571</v>
+        <v>0</v>
       </c>
       <c r="M16" s="14">
-        <v>-26.086956521739</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="N16" s="14">
-        <v>-77.333333333333</v>
+        <v>-78.313253012048</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>60</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>76.923076923076</v>
+        <v>80</v>
       </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J17" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K17" s="14">
-        <v>63.636363636363</v>
+        <v>76</v>
       </c>
       <c r="L17" s="14">
-        <v>200</v>
+        <v>214.285714285714</v>
       </c>
       <c r="M17" s="14">
-        <v>140</v>
+        <v>158.823529411765</v>
       </c>
       <c r="N17" s="14">
-        <v>50</v>
+        <v>69.230769230769</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,10 +1028,10 @@
         <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
         <v>5</v>
@@ -1046,10 +1046,10 @@
         <v>-28.571428571428</v>
       </c>
       <c r="M18" s="14">
-        <v>-86.486486486486</v>
+        <v>-88.095238095238</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.382022471910</v>
+        <v>-94.791666666666</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
         <v>18</v>
       </c>
       <c r="G19" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J19" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K19" s="14">
-        <v>-3.846153846153</v>
+        <v>3.571428571428</v>
       </c>
       <c r="L19" s="14">
-        <v>-43.181818181818</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="M19" s="14">
-        <v>-16.666666666666</v>
+        <v>-9.375</v>
       </c>
       <c r="N19" s="14">
-        <v>-46.808510638297</v>
+        <v>-44.230769230769</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>5</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G20" s="15">
         <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>-36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J20" s="15">
         <v>15</v>
       </c>
       <c r="K20" s="14">
-        <v>-20</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>-42.857142857142</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="M20" s="14">
-        <v>-33.333333333333</v>
+        <v>-15</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.890410958904</v>
+        <v>-94.970414201183</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E21" s="18">
-        <v>37.5</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F21" s="17">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H21" s="18">
-        <v>24.074074074074</v>
+        <v>44.230769230769</v>
       </c>
       <c r="I21" s="17">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="J21" s="17">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K21" s="18">
-        <v>15.476190476190</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.020202020202</v>
+        <v>3.603603603603</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.138211382113</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.663516068052</v>
+        <v>-80.737018425460</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1</v>
+      </c>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
+        <v>1</v>
+      </c>
+      <c r="J22" s="15">
+        <v>1</v>
+      </c>
+      <c r="K22" s="14">
+        <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="M22" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="15">
         <v>12</v>
       </c>
       <c r="G23" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I23" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J23" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L23" s="14">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="M23" s="14">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E24" s="14">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F24" s="15">
         <v>41</v>
       </c>
       <c r="G24" s="15">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H24" s="14">
-        <v>0</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="I24" s="15">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J24" s="15">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K24" s="14">
-        <v>21.052631578947</v>
+        <v>26.153846153846</v>
       </c>
       <c r="L24" s="14">
-        <v>0</v>
+        <v>7.894736842105</v>
       </c>
       <c r="M24" s="14">
-        <v>40.816326530612</v>
+        <v>54.716981132075</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1312,25 +1312,25 @@
         <v>-66.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G25" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H25" s="14">
-        <v>75</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K25" s="14">
-        <v>5.882352941176</v>
+        <v>-5</v>
       </c>
       <c r="L25" s="14">
-        <v>-10</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>80</v>
+        <v>-10</v>
       </c>
       <c r="F26" s="15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G26" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H26" s="14">
-        <v>45.454545454545</v>
+        <v>8</v>
       </c>
       <c r="I26" s="15">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J26" s="15">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K26" s="14">
-        <v>35.135135135135</v>
+        <v>23.404255319148</v>
       </c>
       <c r="L26" s="14">
-        <v>16.279069767441</v>
+        <v>16</v>
       </c>
       <c r="M26" s="14">
-        <v>6.382978723404</v>
+        <v>9.433962264150</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,19 +1397,19 @@
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>66.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L28" s="14">
         <v>66.666666666666</v>

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
@@ -919,8 +919,8 @@
       <c r="K15" s="14">
         <v>-60</v>
       </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+      <c r="L15" s="14">
+        <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
+        <v>5</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-60</v>
       </c>
       <c r="F16" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>180</v>
+        <v>37.5</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J16" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K16" s="14">
-        <v>50</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L16" s="14">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M16" s="14">
-        <v>-37.931034482758</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="N16" s="14">
-        <v>-78.313253012048</v>
+        <v>-78.260869565217</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,10 +978,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="F17" s="15">
         <v>27</v>
@@ -993,22 +993,22 @@
         <v>80</v>
       </c>
       <c r="I17" s="15">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J17" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K17" s="14">
-        <v>76</v>
+        <v>75.862068965517</v>
       </c>
       <c r="L17" s="14">
-        <v>214.285714285714</v>
+        <v>168.421052631579</v>
       </c>
       <c r="M17" s="14">
-        <v>158.823529411765</v>
+        <v>155</v>
       </c>
       <c r="N17" s="14">
-        <v>69.230769230769</v>
+        <v>88.888888888888</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18" s="14">
         <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="14">
-        <v>-88.095238095238</v>
+        <v>-86.363636363636</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.791666666666</v>
+        <v>-94.545454545454</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H19" s="14">
-        <v>12.5</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I19" s="15">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J19" s="15">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K19" s="14">
-        <v>3.571428571428</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="L19" s="14">
-        <v>-38.297872340425</v>
+        <v>-33.962264150943</v>
       </c>
       <c r="M19" s="14">
-        <v>-9.375</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="N19" s="14">
-        <v>-44.230769230769</v>
+        <v>-41.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>3</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
+        <v>42.857142857142</v>
+      </c>
+      <c r="I20" s="15">
+        <v>18</v>
+      </c>
+      <c r="J20" s="15">
+        <v>18</v>
+      </c>
+      <c r="K20" s="14">
         <v>0</v>
       </c>
-      <c r="I20" s="15">
-        <v>17</v>
-      </c>
-      <c r="J20" s="15">
-        <v>15</v>
-      </c>
-      <c r="K20" s="14">
-        <v>13.333333333333</v>
-      </c>
       <c r="L20" s="14">
-        <v>-29.166666666666</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="14">
-        <v>-15</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.970414201183</v>
+        <v>-95.212765957446</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>166.666666666667</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H21" s="18">
-        <v>44.230769230769</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I21" s="17">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="J21" s="17">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="K21" s="18">
-        <v>27.777777777777</v>
+        <v>17.857142857142</v>
       </c>
       <c r="L21" s="18">
-        <v>3.603603603603</v>
+        <v>6.451612903225</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.857142857142</v>
+        <v>-12</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.737018425460</v>
+        <v>-80.209895052473</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -1224,34 +1224,34 @@
         <v>2</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
         <v>12</v>
       </c>
       <c r="G23" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I23" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J23" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K23" s="14">
-        <v>5.882352941176</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L23" s="14">
-        <v>12.5</v>
+        <v>17.647058823529</v>
       </c>
       <c r="M23" s="14">
-        <v>500</v>
+        <v>566.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D24" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E24" s="14">
-        <v>62.5</v>
+        <v>-75</v>
       </c>
       <c r="F24" s="15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G24" s="15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H24" s="14">
-        <v>-4.651162790697</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I24" s="15">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J24" s="15">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K24" s="14">
-        <v>26.153846153846</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L24" s="14">
-        <v>7.894736842105</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M24" s="14">
-        <v>54.716981132075</v>
+        <v>35.483870967741</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15">
         <v>3</v>
       </c>
-      <c r="E25" s="14">
-        <v>-66.666666666666</v>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
+        <v>7</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
+        <v>22</v>
+      </c>
+      <c r="J25" s="15">
+        <v>20</v>
+      </c>
+      <c r="K25" s="14">
         <v>10</v>
       </c>
-      <c r="H25" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I25" s="15">
-        <v>19</v>
-      </c>
-      <c r="J25" s="15">
-        <v>20</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-5</v>
-      </c>
       <c r="L25" s="14">
-        <v>-13.636363636363</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>6</v>
+      </c>
+      <c r="D26" s="15">
         <v>9</v>
       </c>
-      <c r="D26" s="15">
-        <v>10</v>
-      </c>
       <c r="E26" s="14">
-        <v>-10</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>8</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I26" s="15">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J26" s="15">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K26" s="14">
-        <v>23.404255319148</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L26" s="14">
-        <v>16</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M26" s="14">
-        <v>9.433962264150</v>
+        <v>18.518518518518</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
@@ -1411,8 +1411,8 @@
       <c r="K27" s="14">
         <v>-66.666666666666</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
+      <c r="L27" s="14">
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="15">
         <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>11.111111111111</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L28" s="14">
-        <v>66.666666666666</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>-50</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+        <v>200</v>
+      </c>
+      <c r="M15" s="14">
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>5</v>
+      </c>
+      <c r="D16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>5</v>
-      </c>
       <c r="E16" s="14">
-        <v>-60</v>
+        <v>150</v>
       </c>
       <c r="F16" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>37.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J16" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K16" s="14">
-        <v>17.647058823529</v>
+        <v>31.578947368421</v>
       </c>
       <c r="L16" s="14">
-        <v>11.111111111111</v>
+        <v>31.578947368421</v>
       </c>
       <c r="M16" s="14">
-        <v>-31.034482758620</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="N16" s="14">
-        <v>-78.260869565217</v>
+        <v>-76.635514018691</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,54 +975,54 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>80</v>
+        <v>77.777777777777</v>
       </c>
       <c r="I17" s="15">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J17" s="15">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K17" s="14">
-        <v>75.862068965517</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L17" s="14">
-        <v>168.421052631579</v>
+        <v>172.727272727273</v>
       </c>
       <c r="M17" s="14">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="N17" s="14">
-        <v>88.888888888888</v>
+        <v>106.896551724138</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
         <v>1</v>
@@ -1034,22 +1034,22 @@
         <v>-50</v>
       </c>
       <c r="I18" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J18" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" s="14">
         <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M18" s="14">
-        <v>-86.363636363636</v>
+        <v>-84.444444444444</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.545454545454</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="F19" s="15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H19" s="14">
-        <v>-4.761904761904</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I19" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J19" s="15">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K19" s="14">
-        <v>-5.405405405405</v>
+        <v>-20</v>
       </c>
       <c r="L19" s="14">
-        <v>-33.962264150943</v>
+        <v>-40</v>
       </c>
       <c r="M19" s="14">
-        <v>-2.777777777777</v>
+        <v>-10</v>
       </c>
       <c r="N19" s="14">
-        <v>-41.666666666666</v>
+        <v>-44.615384615384</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F20" s="15">
         <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>42.857142857142</v>
+        <v>25</v>
       </c>
       <c r="I20" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J20" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K20" s="14">
+        <v>5</v>
+      </c>
+      <c r="L20" s="14">
+        <v>-16</v>
+      </c>
+      <c r="M20" s="14">
         <v>0</v>
       </c>
-      <c r="L20" s="14">
-        <v>-25</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-14.285714285714</v>
-      </c>
       <c r="N20" s="14">
-        <v>-95.212765957446</v>
+        <v>-94.964028776978</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-27.272727272727</v>
+        <v>5.263157894736</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>27.272727272727</v>
+        <v>20.634920634920</v>
       </c>
       <c r="I21" s="17">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="J21" s="17">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="K21" s="18">
-        <v>17.857142857142</v>
+        <v>16.030534351145</v>
       </c>
       <c r="L21" s="18">
-        <v>6.451612903225</v>
+        <v>10.948905109489</v>
       </c>
       <c r="M21" s="18">
-        <v>-12</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.209895052473</v>
+        <v>-79.706275033377</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G23" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="14">
-        <v>50</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I23" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J23" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K23" s="14">
-        <v>5.263157894736</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="L23" s="14">
-        <v>17.647058823529</v>
+        <v>23.529411764705</v>
       </c>
       <c r="M23" s="14">
-        <v>566.666666666667</v>
+        <v>600</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
         <v>12</v>
       </c>
       <c r="E24" s="14">
-        <v>-75</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" s="15">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H24" s="14">
-        <v>-4.545454545454</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="I24" s="15">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J24" s="15">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K24" s="14">
-        <v>9.090909090909</v>
+        <v>11.235955056179</v>
       </c>
       <c r="L24" s="14">
-        <v>-3.448275862068</v>
+        <v>2.061855670103</v>
       </c>
       <c r="M24" s="14">
-        <v>35.483870967741</v>
+        <v>30.263157894736</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D25" s="15">
+        <v>2</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I25" s="15">
+        <v>23</v>
+      </c>
+      <c r="J25" s="15">
         <v>22</v>
       </c>
-      <c r="J25" s="15">
-        <v>20</v>
-      </c>
       <c r="K25" s="14">
-        <v>10</v>
+        <v>4.545454545454</v>
       </c>
       <c r="L25" s="14">
-        <v>-4.347826086956</v>
+        <v>-8</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>7</v>
+      </c>
+      <c r="D26" s="15">
         <v>6</v>
       </c>
-      <c r="D26" s="15">
-        <v>9</v>
-      </c>
       <c r="E26" s="14">
-        <v>-33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G26" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H26" s="14">
-        <v>-3.448275862068</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J26" s="15">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K26" s="14">
-        <v>14.285714285714</v>
+        <v>14.516129032258</v>
       </c>
       <c r="L26" s="14">
-        <v>14.285714285714</v>
+        <v>20.338983050847</v>
       </c>
       <c r="M26" s="14">
-        <v>18.518518518518</v>
+        <v>10.9375</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
         <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
         <v>11</v>
       </c>
       <c r="J28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="L28" s="14">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="15">
+        <v>4</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="15">
+        <v>4</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,31 +1484,31 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="15">
+        <v>4</v>
       </c>
       <c r="J29" s="15">
         <v>1</v>
       </c>
       <c r="K29" s="14">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="L29" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="M29" s="14">
-        <v>-100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N29" s="14">
-        <v>-100</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="15">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="15">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,23 +1525,23 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="15">
+        <v>1</v>
       </c>
       <c r="J30" s="15">
         <v>1</v>
       </c>
       <c r="K30" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,10 +905,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
@@ -920,13 +920,13 @@
         <v>-40</v>
       </c>
       <c r="L15" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M15" s="14">
         <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>66.666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="I16" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="14">
-        <v>31.578947368421</v>
+        <v>30</v>
       </c>
       <c r="L16" s="14">
-        <v>31.578947368421</v>
+        <v>30</v>
       </c>
       <c r="M16" s="14">
-        <v>-30.555555555555</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-76.635514018691</v>
+        <v>-76.991150442477</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
         <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>77.777777777777</v>
+        <v>26.315789473684</v>
       </c>
       <c r="I17" s="15">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J17" s="15">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K17" s="14">
-        <v>71.428571428571</v>
+        <v>48.780487804878</v>
       </c>
       <c r="L17" s="14">
-        <v>172.727272727273</v>
+        <v>144</v>
       </c>
       <c r="M17" s="14">
-        <v>140</v>
+        <v>96.774193548387</v>
       </c>
       <c r="N17" s="14">
-        <v>106.896551724138</v>
+        <v>90.625</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>0</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="15">
         <v>2</v>
       </c>
       <c r="H18" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" s="15">
         <v>7</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L18" s="14">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M18" s="14">
-        <v>-84.444444444444</v>
+        <v>-82.608695652173</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.444444444444</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>-75</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F19" s="15">
         <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H19" s="14">
-        <v>-29.166666666666</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I19" s="15">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J19" s="15">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K19" s="14">
-        <v>-20</v>
+        <v>-10.416666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>-40</v>
+        <v>-37.681159420289</v>
       </c>
       <c r="M19" s="14">
-        <v>-10</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="N19" s="14">
-        <v>-44.615384615384</v>
+        <v>-43.421052631578</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F20" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
+        <v>85.714285714285</v>
+      </c>
+      <c r="I20" s="15">
         <v>25</v>
       </c>
-      <c r="I20" s="15">
-        <v>21</v>
-      </c>
       <c r="J20" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K20" s="14">
-        <v>5</v>
+        <v>13.636363636363</v>
       </c>
       <c r="L20" s="14">
-        <v>-16</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>19.047619047619</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.964028776978</v>
+        <v>-94.469026548672</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>5.263157894736</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H21" s="18">
-        <v>20.634920634920</v>
+        <v>11.864406779661</v>
       </c>
       <c r="I21" s="17">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J21" s="17">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="K21" s="18">
-        <v>16.030534351145</v>
+        <v>16.083916083916</v>
       </c>
       <c r="L21" s="18">
-        <v>10.948905109489</v>
+        <v>7.792207792207</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.523809523809</v>
+        <v>-9.289617486338</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.706275033377</v>
+        <v>-79.631901840490</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="15">
+        <v>6</v>
+      </c>
+      <c r="G23" s="15">
         <v>8</v>
       </c>
-      <c r="G23" s="15">
-        <v>9</v>
-      </c>
       <c r="H23" s="14">
-        <v>-11.111111111111</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K23" s="14">
-        <v>-4.545454545454</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>23.529411764705</v>
+        <v>15.789473684210</v>
       </c>
       <c r="M23" s="14">
-        <v>600</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E24" s="14">
-        <v>8.333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="F24" s="15">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G24" s="15">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H24" s="14">
-        <v>-4.651162790697</v>
+        <v>7.5</v>
       </c>
       <c r="I24" s="15">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="J24" s="15">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K24" s="14">
-        <v>11.235955056179</v>
+        <v>15.463917525773</v>
       </c>
       <c r="L24" s="14">
-        <v>2.061855670103</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M24" s="14">
-        <v>30.263157894736</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>3</v>
+      </c>
+      <c r="D25" s="15">
         <v>1</v>
       </c>
-      <c r="D25" s="15">
-        <v>2</v>
-      </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F25" s="15">
+        <v>8</v>
+      </c>
+      <c r="G25" s="15">
         <v>6</v>
       </c>
-      <c r="G25" s="15">
-        <v>8</v>
-      </c>
       <c r="H25" s="14">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I25" s="15">
+        <v>26</v>
+      </c>
+      <c r="J25" s="15">
         <v>23</v>
       </c>
-      <c r="J25" s="15">
-        <v>22</v>
-      </c>
       <c r="K25" s="14">
-        <v>4.545454545454</v>
+        <v>13.043478260869</v>
       </c>
       <c r="L25" s="14">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>16.666666666666</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F26" s="15">
         <v>30</v>
       </c>
       <c r="G26" s="15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J26" s="15">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K26" s="14">
-        <v>14.516129032258</v>
+        <v>8.219178082191</v>
       </c>
       <c r="L26" s="14">
-        <v>20.338983050847</v>
+        <v>21.538461538461</v>
       </c>
       <c r="M26" s="14">
-        <v>10.9375</v>
+        <v>1.282051282051</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>3</v>
@@ -1412,7 +1412,7 @@
         <v>-57.142857142857</v>
       </c>
       <c r="L27" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,22 +1438,22 @@
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="15">
         <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L28" s="14">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
-        <v>4</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1494,7 +1494,7 @@
         <v>300</v>
       </c>
       <c r="L29" s="14">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M29" s="14">
         <v>33.333333333333</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="14">
         <v>-50</v>

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -884,8 +884,8 @@
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="13" t="s">
-        <v>21</v>
+      <c r="N14" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -904,11 +904,11 @@
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
@@ -923,7 +923,7 @@
         <v>50</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N15" s="14">
         <v>-50</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
+        <v>-25</v>
+      </c>
+      <c r="F16" s="15">
+        <v>12</v>
+      </c>
+      <c r="G16" s="15">
+        <v>12</v>
+      </c>
+      <c r="H16" s="14">
         <v>0</v>
       </c>
-      <c r="F16" s="15">
-        <v>9</v>
-      </c>
-      <c r="G16" s="15">
-        <v>8</v>
-      </c>
-      <c r="H16" s="14">
-        <v>12.5</v>
-      </c>
       <c r="I16" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J16" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K16" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L16" s="14">
-        <v>30</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M16" s="14">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="N16" s="14">
-        <v>-76.991150442477</v>
+        <v>-75.806451612903</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-83.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>26.315789473684</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J17" s="15">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K17" s="14">
-        <v>48.780487804878</v>
+        <v>46.511627906976</v>
       </c>
       <c r="L17" s="14">
-        <v>144</v>
+        <v>90.909090909090</v>
       </c>
       <c r="M17" s="14">
-        <v>96.774193548387</v>
+        <v>90.909090909090</v>
       </c>
       <c r="N17" s="14">
-        <v>90.625</v>
+        <v>61.538461538461</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="15">
+        <v>2</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
+        <v>-25</v>
+      </c>
+      <c r="I18" s="15">
+        <v>9</v>
+      </c>
+      <c r="J18" s="15">
+        <v>9</v>
+      </c>
+      <c r="K18" s="14">
         <v>0</v>
       </c>
-      <c r="I18" s="15">
-        <v>8</v>
-      </c>
-      <c r="J18" s="15">
-        <v>7</v>
-      </c>
-      <c r="K18" s="14">
-        <v>14.285714285714</v>
-      </c>
       <c r="L18" s="14">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="14">
-        <v>-82.608695652173</v>
+        <v>-81.632653061224</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.117647058823</v>
+        <v>-93.793103448275</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>133.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="15">
         <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>-22.727272727272</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="I19" s="15">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J19" s="15">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K19" s="14">
-        <v>-10.416666666666</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L19" s="14">
-        <v>-37.681159420289</v>
+        <v>-37.837837837837</v>
       </c>
       <c r="M19" s="14">
-        <v>-4.444444444444</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>-43.421052631578</v>
+        <v>-45.238095238095</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F20" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H20" s="14">
-        <v>85.714285714285</v>
+        <v>50</v>
       </c>
       <c r="I20" s="15">
+        <v>32</v>
+      </c>
+      <c r="J20" s="15">
         <v>25</v>
       </c>
-      <c r="J20" s="15">
-        <v>22</v>
-      </c>
       <c r="K20" s="14">
-        <v>13.636363636363</v>
+        <v>28</v>
       </c>
       <c r="L20" s="14">
-        <v>-10.714285714285</v>
+        <v>10.344827586206</v>
       </c>
       <c r="M20" s="14">
-        <v>19.047619047619</v>
+        <v>39.130434782608</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.469026548672</v>
+        <v>-93.495934959349</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>16.666666666666</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F21" s="17">
         <v>66</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
-        <v>11.864406779661</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="I21" s="17">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="J21" s="17">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="K21" s="18">
-        <v>16.083916083916</v>
+        <v>14.375</v>
       </c>
       <c r="L21" s="18">
-        <v>7.792207792207</v>
+        <v>6.395348837209</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.289617486338</v>
+        <v>-6.153846153846</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.631901840490</v>
+        <v>-79.484304932735</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M22" s="14">
         <v>-50</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="15">
         <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
         <v>6</v>
       </c>
       <c r="G23" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J23" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K23" s="14">
-        <v>-8.333333333333</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L23" s="14">
-        <v>15.789473684210</v>
+        <v>19.047619047619</v>
       </c>
       <c r="M23" s="14">
-        <v>266.666666666667</v>
+        <v>257.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D24" s="15">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
-        <v>62.5</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="F24" s="15">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G24" s="15">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H24" s="14">
-        <v>7.5</v>
+        <v>-29.090909090909</v>
       </c>
       <c r="I24" s="15">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="J24" s="15">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="K24" s="14">
-        <v>15.463917525773</v>
+        <v>0.833333333333</v>
       </c>
       <c r="L24" s="14">
-        <v>7.692307692307</v>
+        <v>6.140350877192</v>
       </c>
       <c r="M24" s="14">
-        <v>33.333333333333</v>
+        <v>31.521739130434</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,31 +1303,31 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>200</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F25" s="15">
         <v>8</v>
       </c>
       <c r="G25" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H25" s="14">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J25" s="15">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="K25" s="14">
-        <v>13.043478260869</v>
+        <v>-10</v>
       </c>
       <c r="L25" s="14">
         <v>0</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>-27.272727272727</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H26" s="14">
-        <v>-16.666666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I26" s="15">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J26" s="15">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K26" s="14">
-        <v>8.219178082191</v>
+        <v>10.666666666666</v>
       </c>
       <c r="L26" s="14">
-        <v>21.538461538461</v>
+        <v>10.666666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>1.282051282051</v>
+        <v>-7.777777777777</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="15">
         <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L27" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
-      </c>
-      <c r="G28" s="15">
         <v>3</v>
       </c>
-      <c r="H28" s="14">
-        <v>-33.333333333333</v>
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="15">
         <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L28" s="14">
-        <v>71.428571428571</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>300</v>
       </c>
       <c r="L29" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M29" s="14">
         <v>33.333333333333</v>
       </c>
       <c r="N29" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M30" s="14">
         <v>-50</v>
       </c>
       <c r="N30" s="14">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15">
         <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N15" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
         <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
         <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I16" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J16" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K16" s="14">
-        <v>25</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L16" s="14">
-        <v>36.363636363636</v>
+        <v>39.130434782608</v>
       </c>
       <c r="M16" s="14">
-        <v>-25</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="N16" s="14">
-        <v>-75.806451612903</v>
+        <v>-76.470588235294</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,54 +975,54 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G17" s="15">
         <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J17" s="15">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K17" s="14">
-        <v>46.511627906976</v>
+        <v>36.170212765957</v>
       </c>
       <c r="L17" s="14">
-        <v>90.909090909090</v>
+        <v>52.380952380952</v>
       </c>
       <c r="M17" s="14">
-        <v>90.909090909090</v>
+        <v>68.421052631578</v>
       </c>
       <c r="N17" s="14">
-        <v>61.538461538461</v>
+        <v>52.380952380952</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>3</v>
@@ -1037,19 +1037,19 @@
         <v>9</v>
       </c>
       <c r="J18" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L18" s="14">
         <v>-10</v>
       </c>
       <c r="M18" s="14">
-        <v>-81.632653061224</v>
+        <v>-83.018867924528</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.793103448275</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15">
         <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G19" s="15">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H19" s="14">
-        <v>-34.615384615384</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="I19" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J19" s="15">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K19" s="14">
-        <v>-14.814814814814</v>
+        <v>-21.666666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>-37.837837837837</v>
+        <v>-38.961038961039</v>
       </c>
       <c r="M19" s="14">
-        <v>-4.166666666666</v>
+        <v>-9.615384615384</v>
       </c>
       <c r="N19" s="14">
-        <v>-45.238095238095</v>
+        <v>-47.191011235955</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>7</v>
-      </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>133.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
         <v>15</v>
       </c>
       <c r="G20" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>50</v>
+        <v>114.285714285714</v>
       </c>
       <c r="I20" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J20" s="15">
         <v>25</v>
       </c>
       <c r="K20" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L20" s="14">
-        <v>10.344827586206</v>
+        <v>6.451612903225</v>
       </c>
       <c r="M20" s="14">
-        <v>39.130434782608</v>
+        <v>37.5</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.495934959349</v>
+        <v>-93.866171003717</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.882352941176</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G21" s="17">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.714285714285</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I21" s="17">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J21" s="17">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="K21" s="18">
-        <v>14.375</v>
+        <v>8</v>
       </c>
       <c r="L21" s="18">
-        <v>6.395348837209</v>
+        <v>1.069518716577</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.153846153846</v>
+        <v>-11.682242990654</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.484304932735</v>
+        <v>-80.615384615384</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>-80</v>
       </c>
       <c r="M22" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
         <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23" s="15">
         <v>9</v>
       </c>
       <c r="H23" s="14">
-        <v>-33.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I23" s="15">
         <v>25</v>
       </c>
       <c r="J23" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K23" s="14">
-        <v>-3.846153846153</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L23" s="14">
-        <v>19.047619047619</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>257.142857142857</v>
+        <v>150</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>-60.869565217391</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="15">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G24" s="15">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H24" s="14">
-        <v>-29.090909090909</v>
+        <v>-20.338983050847</v>
       </c>
       <c r="I24" s="15">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J24" s="15">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="K24" s="14">
-        <v>0.833333333333</v>
+        <v>-2.205882352941</v>
       </c>
       <c r="L24" s="14">
-        <v>6.140350877192</v>
+        <v>9.016393442622</v>
       </c>
       <c r="M24" s="14">
-        <v>31.521739130434</v>
+        <v>29.126213592233</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,31 +1303,31 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
+        <v>3</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F25" s="15">
         <v>7</v>
       </c>
-      <c r="E25" s="14">
-        <v>-85.714285714285</v>
-      </c>
-      <c r="F25" s="15">
-        <v>8</v>
-      </c>
       <c r="G25" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H25" s="14">
-        <v>-20</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I25" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J25" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K25" s="14">
-        <v>-10</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="L25" s="14">
         <v>0</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
         <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H26" s="14">
-        <v>-7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J26" s="15">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K26" s="14">
-        <v>10.666666666666</v>
+        <v>9.756097560975</v>
       </c>
       <c r="L26" s="14">
-        <v>10.666666666666</v>
+        <v>18.421052631578</v>
       </c>
       <c r="M26" s="14">
-        <v>-7.777777777777</v>
+        <v>-6.25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
         <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L27" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,7 +1435,7 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>20</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="15">
+        <v>2</v>
+      </c>
+      <c r="E29" s="14">
+        <v>-100</v>
       </c>
       <c r="F29" s="15">
         <v>4</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="15">
+        <v>2</v>
+      </c>
+      <c r="H29" s="14">
+        <v>100</v>
       </c>
       <c r="I29" s="15">
         <v>4</v>
       </c>
       <c r="J29" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="14">
-        <v>300</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L29" s="14">
         <v>0</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="15">
+        <v>2</v>
+      </c>
+      <c r="E30" s="14">
+        <v>-100</v>
       </c>
       <c r="F30" s="15">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="15">
+        <v>2</v>
+      </c>
+      <c r="H30" s="14">
+        <v>-50</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
       </c>
       <c r="J30" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="14">
         <v>-75</v>

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
         <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M15" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N15" s="14">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
+        <v>9</v>
+      </c>
+      <c r="G16" s="15">
         <v>12</v>
       </c>
-      <c r="G16" s="15">
-        <v>11</v>
-      </c>
       <c r="H16" s="14">
-        <v>9.090909090909</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J16" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>14.285714285714</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L16" s="14">
-        <v>39.130434782608</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M16" s="14">
-        <v>-28.888888888888</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="N16" s="14">
-        <v>-76.470588235294</v>
+        <v>-77.483443708609</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J17" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K17" s="14">
-        <v>36.170212765957</v>
+        <v>30</v>
       </c>
       <c r="L17" s="14">
-        <v>52.380952380952</v>
+        <v>30</v>
       </c>
       <c r="M17" s="14">
-        <v>68.421052631578</v>
+        <v>58.536585365853</v>
       </c>
       <c r="N17" s="14">
-        <v>52.380952380952</v>
+        <v>38.297872340425</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,20 +1018,20 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
+        <v>2</v>
+      </c>
+      <c r="G18" s="15">
         <v>3</v>
       </c>
-      <c r="G18" s="15">
-        <v>4</v>
-      </c>
       <c r="H18" s="14">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="15">
         <v>9</v>
@@ -1046,10 +1046,10 @@
         <v>-10</v>
       </c>
       <c r="M18" s="14">
-        <v>-83.018867924528</v>
+        <v>-83.928571428571</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.444444444444</v>
+        <v>-94.767441860465</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>-66.666666666666</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H19" s="14">
-        <v>-43.478260869565</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="I19" s="15">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J19" s="15">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="K19" s="14">
-        <v>-21.666666666666</v>
+        <v>-26.388888888888</v>
       </c>
       <c r="L19" s="14">
-        <v>-38.961038961039</v>
+        <v>-36.904761904761</v>
       </c>
       <c r="M19" s="14">
-        <v>-9.615384615384</v>
+        <v>-7.017543859649</v>
       </c>
       <c r="N19" s="14">
-        <v>-47.191011235955</v>
+        <v>-46.464646464646</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,7 +1098,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>114.285714285714</v>
+        <v>180</v>
       </c>
       <c r="I20" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J20" s="15">
         <v>25</v>
       </c>
       <c r="K20" s="14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L20" s="14">
-        <v>6.451612903225</v>
+        <v>6.060606060606</v>
       </c>
       <c r="M20" s="14">
-        <v>37.5</v>
+        <v>34.615384615384</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.866171003717</v>
+        <v>-93.913043478260</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-53.333333333333</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F21" s="17">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.523809523809</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="I21" s="17">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="J21" s="17">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="K21" s="18">
-        <v>8</v>
+        <v>4.145077720207</v>
       </c>
       <c r="L21" s="18">
-        <v>1.069518716577</v>
+        <v>-1.951219512195</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.682242990654</v>
+        <v>-11.842105263157</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.615384615384</v>
+        <v>-80.911680911680</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H23" s="14">
-        <v>-55.555555555555</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I23" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J23" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K23" s="14">
-        <v>-10.714285714285</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L23" s="14">
-        <v>4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="M23" s="14">
-        <v>150</v>
+        <v>136.363636363636</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E24" s="14">
-        <v>-25</v>
+        <v>212.5</v>
       </c>
       <c r="F24" s="15">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G24" s="15">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H24" s="14">
-        <v>-20.338983050847</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I24" s="15">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="J24" s="15">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="K24" s="14">
-        <v>-2.205882352941</v>
+        <v>9.722222222222</v>
       </c>
       <c r="L24" s="14">
-        <v>9.016393442622</v>
+        <v>19.696969696969</v>
       </c>
       <c r="M24" s="14">
-        <v>29.126213592233</v>
+        <v>43.636363636363</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14">
-        <v>-33.333333333333</v>
+        <v>400</v>
       </c>
       <c r="F25" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G25" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H25" s="14">
-        <v>-46.153846153846</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J25" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K25" s="14">
-        <v>-12.121212121212</v>
+        <v>0</v>
       </c>
       <c r="L25" s="14">
-        <v>0</v>
+        <v>9.677419354838</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G26" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="I26" s="15">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J26" s="15">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K26" s="14">
-        <v>9.756097560975</v>
+        <v>2.197802197802</v>
       </c>
       <c r="L26" s="14">
-        <v>18.421052631578</v>
+        <v>13.414634146341</v>
       </c>
       <c r="M26" s="14">
-        <v>-6.25</v>
+        <v>-10.576923076923</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,23 +1396,23 @@
       <c r="F27" s="15">
         <v>3</v>
       </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>200</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
         <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L27" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="14">
+        <v>200</v>
       </c>
       <c r="I28" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>30</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L28" s="14">
-        <v>44.444444444444</v>
+        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="15">
-        <v>2</v>
-      </c>
-      <c r="E29" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="15">
-        <v>4</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="15">
         <v>2</v>
       </c>
       <c r="H29" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="15">
         <v>4</v>
@@ -1500,7 +1500,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="N29" s="14">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="15">
-        <v>2</v>
-      </c>
-      <c r="E30" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="15">
         <v>2</v>
       </c>
       <c r="H30" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1575,8 +1575,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="14">
+        <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>200</v>
       </c>
       <c r="I15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="14">
         <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="15">
         <v>3</v>
       </c>
-      <c r="E16" s="14">
-        <v>-33.333333333333</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H16" s="14">
-        <v>-25</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I16" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J16" s="15">
         <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>9.677419354838</v>
+        <v>19.354838709677</v>
       </c>
       <c r="L16" s="14">
-        <v>41.666666666666</v>
+        <v>48</v>
       </c>
       <c r="M16" s="14">
-        <v>-26.086956521739</v>
+        <v>-22.916666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-77.483443708609</v>
+        <v>-77.018633540372</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,48 +975,48 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
         <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>-66.666666666666</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J17" s="15">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K17" s="14">
-        <v>30</v>
+        <v>28.301886792452</v>
       </c>
       <c r="L17" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M17" s="14">
-        <v>58.536585365853</v>
+        <v>58.139534883720</v>
       </c>
       <c r="N17" s="14">
-        <v>38.297872340425</v>
+        <v>13.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1034,22 +1034,22 @@
         <v>-33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J18" s="15">
         <v>10</v>
       </c>
       <c r="K18" s="14">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M18" s="14">
-        <v>-83.928571428571</v>
+        <v>-84.126984126984</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.767441860465</v>
+        <v>-94.623655913978</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>7</v>
+      </c>
+      <c r="D19" s="15">
         <v>5</v>
       </c>
-      <c r="D19" s="15">
-        <v>12</v>
-      </c>
       <c r="E19" s="14">
-        <v>-58.333333333333</v>
+        <v>40</v>
       </c>
       <c r="F19" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>-37.037037037037</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="I19" s="15">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J19" s="15">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K19" s="14">
-        <v>-26.388888888888</v>
+        <v>-22.077922077922</v>
       </c>
       <c r="L19" s="14">
-        <v>-36.904761904761</v>
+        <v>-32.584269662921</v>
       </c>
       <c r="M19" s="14">
-        <v>-7.017543859649</v>
+        <v>3.448275862068</v>
       </c>
       <c r="N19" s="14">
-        <v>-46.464646464646</v>
+        <v>-42.307692307692</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="14">
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G20" s="15">
         <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I20" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K20" s="14">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="14">
-        <v>6.060606060606</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M20" s="14">
-        <v>34.615384615384</v>
+        <v>20</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.913043478260</v>
+        <v>-94.221508828250</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>15</v>
+      </c>
+      <c r="D21" s="17">
         <v>11</v>
       </c>
-      <c r="D21" s="17">
-        <v>18</v>
-      </c>
       <c r="E21" s="18">
-        <v>-38.888888888888</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.967741935483</v>
+        <v>-16.393442622950</v>
       </c>
       <c r="I21" s="17">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="J21" s="17">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="K21" s="18">
-        <v>4.145077720207</v>
+        <v>6.372549019607</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.951219512195</v>
+        <v>1.401869158878</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.842105263157</v>
+        <v>-11.065573770491</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.911680911680</v>
+        <v>-81.014873140857</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="15">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="15">
         <v>1</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="14">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M22" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="15">
         <v>7</v>
       </c>
       <c r="H23" s="14">
-        <v>-28.571428571428</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I23" s="15">
         <v>26</v>
       </c>
       <c r="J23" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K23" s="14">
-        <v>-10.344827586206</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="M23" s="14">
         <v>136.363636363636</v>
@@ -1265,34 +1265,34 @@
         <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>212.5</v>
+        <v>92.307692307692</v>
       </c>
       <c r="F24" s="15">
+        <v>69</v>
+      </c>
+      <c r="G24" s="15">
         <v>60</v>
       </c>
-      <c r="G24" s="15">
-        <v>55</v>
-      </c>
       <c r="H24" s="14">
-        <v>9.090909090909</v>
+        <v>15</v>
       </c>
       <c r="I24" s="15">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="J24" s="15">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="K24" s="14">
-        <v>9.722222222222</v>
+        <v>15.286624203821</v>
       </c>
       <c r="L24" s="14">
-        <v>19.696969696969</v>
+        <v>29.285714285714</v>
       </c>
       <c r="M24" s="14">
-        <v>43.636363636363</v>
+        <v>49.586776859504</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>400</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="15">
         <v>11</v>
       </c>
       <c r="G25" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H25" s="14">
-        <v>-8.333333333333</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J25" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K25" s="14">
-        <v>0</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="L25" s="14">
-        <v>9.677419354838</v>
+        <v>19.354838709677</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>-66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F26" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G26" s="15">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H26" s="14">
-        <v>-24.137931034482</v>
+        <v>-4</v>
       </c>
       <c r="I26" s="15">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J26" s="15">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K26" s="14">
-        <v>2.197802197802</v>
+        <v>5.102040816326</v>
       </c>
       <c r="L26" s="14">
-        <v>13.414634146341</v>
+        <v>21.176470588235</v>
       </c>
       <c r="M26" s="14">
-        <v>-10.576923076923</v>
+        <v>-10.434782608695</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
       </c>
       <c r="I27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="L27" s="14">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,11 +1428,11 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>3</v>
@@ -1444,16 +1444,16 @@
         <v>200</v>
       </c>
       <c r="I28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="15">
         <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L28" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N29" s="14">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-75</v>
       </c>
       <c r="M30" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
         <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N15" s="14">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J16" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K16" s="14">
-        <v>19.354838709677</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L16" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="M16" s="14">
-        <v>-22.916666666666</v>
+        <v>-22</v>
       </c>
       <c r="N16" s="14">
-        <v>-77.018633540372</v>
+        <v>-77.714285714285</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
         <v>-33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H17" s="14">
-        <v>-41.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="I17" s="15">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J17" s="15">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K17" s="14">
-        <v>28.301886792452</v>
+        <v>25.423728813559</v>
       </c>
       <c r="L17" s="14">
-        <v>36</v>
+        <v>34.545454545454</v>
       </c>
       <c r="M17" s="14">
-        <v>58.139534883720</v>
+        <v>68.181818181818</v>
       </c>
       <c r="N17" s="14">
-        <v>13.333333333333</v>
+        <v>12.121212121212</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>2</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="15">
+        <v>3</v>
+      </c>
+      <c r="G18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="15">
-        <v>2</v>
-      </c>
-      <c r="G18" s="15">
-        <v>3</v>
-      </c>
       <c r="H18" s="14">
-        <v>-33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="I18" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J18" s="15">
         <v>10</v>
       </c>
       <c r="K18" s="14">
+        <v>20</v>
+      </c>
+      <c r="L18" s="14">
         <v>0</v>
       </c>
-      <c r="L18" s="14">
-        <v>-9.090909090909</v>
-      </c>
       <c r="M18" s="14">
-        <v>-84.126984126984</v>
+        <v>-82.857142857142</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.623655913978</v>
+        <v>-93.939393939393</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="15">
         <v>18</v>
@@ -1075,22 +1075,22 @@
         <v>-37.931034482758</v>
       </c>
       <c r="I19" s="15">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J19" s="15">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K19" s="14">
-        <v>-22.077922077922</v>
+        <v>-24.096385542168</v>
       </c>
       <c r="L19" s="14">
-        <v>-32.584269662921</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M19" s="14">
-        <v>3.448275862068</v>
+        <v>0</v>
       </c>
       <c r="N19" s="14">
-        <v>-42.307692307692</v>
+        <v>-41.121495327102</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>4</v>
+      </c>
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>300</v>
       </c>
       <c r="F20" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>120</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I20" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J20" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" s="14">
-        <v>33.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L20" s="14">
-        <v>5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="M20" s="14">
-        <v>20</v>
+        <v>29.032258064516</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.221508828250</v>
+        <v>-94.047619047619</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,45 +1142,45 @@
         <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.393442622950</v>
+        <v>-15.254237288135</v>
       </c>
       <c r="I21" s="17">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="J21" s="17">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="K21" s="18">
-        <v>6.372549019607</v>
+        <v>6.392694063926</v>
       </c>
       <c r="L21" s="18">
-        <v>1.401869158878</v>
+        <v>-1.271186440677</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.065573770491</v>
+        <v>-10.384615384615</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.014873140857</v>
+        <v>-81.026058631921</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>-60</v>
       </c>
       <c r="M22" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
+        <v>3</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F23" s="15">
         <v>2</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="15">
-        <v>3</v>
-      </c>
       <c r="G23" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="14">
-        <v>-57.142857142857</v>
+        <v>-75</v>
       </c>
       <c r="I23" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K23" s="14">
-        <v>-16.129032258064</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="L23" s="14">
-        <v>-3.703703703703</v>
+        <v>-10</v>
       </c>
       <c r="M23" s="14">
-        <v>136.363636363636</v>
+        <v>125</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E24" s="14">
-        <v>92.307692307692</v>
+        <v>216.666666666667</v>
       </c>
       <c r="F24" s="15">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G24" s="15">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="H24" s="14">
-        <v>15</v>
+        <v>83.720930232558</v>
       </c>
       <c r="I24" s="15">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="J24" s="15">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="K24" s="14">
-        <v>15.286624203821</v>
+        <v>22.699386503067</v>
       </c>
       <c r="L24" s="14">
-        <v>29.285714285714</v>
+        <v>31.578947368421</v>
       </c>
       <c r="M24" s="14">
-        <v>49.586776859504</v>
+        <v>50.375939849624</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" s="15">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H25" s="14">
-        <v>-26.666666666666</v>
+        <v>30</v>
       </c>
       <c r="I25" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J25" s="15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K25" s="14">
-        <v>-2.631578947368</v>
+        <v>0</v>
       </c>
       <c r="L25" s="14">
-        <v>19.354838709677</v>
+        <v>21.212121212121</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>42.857142857142</v>
+        <v>200</v>
       </c>
       <c r="F26" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26" s="15">
         <v>25</v>
       </c>
       <c r="H26" s="14">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J26" s="15">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K26" s="14">
-        <v>5.102040816326</v>
+        <v>8</v>
       </c>
       <c r="L26" s="14">
-        <v>21.176470588235</v>
+        <v>16.129032258064</v>
       </c>
       <c r="M26" s="14">
-        <v>-10.434782608695</v>
+        <v>-8.474576271186</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
         <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-12.5</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="14">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,13 +1435,13 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
         <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
         <v>15</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N29" s="14">
         <v>-55.555555555555</v>
@@ -1538,7 +1538,7 @@
         <v>-75</v>
       </c>
       <c r="M30" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="14">
         <v>-87.5</v>

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -911,63 +911,63 @@
         <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="15">
         <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
         <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I16" s="15">
         <v>39</v>
       </c>
       <c r="J16" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K16" s="14">
-        <v>18.181818181818</v>
+        <v>5.405405405405</v>
       </c>
       <c r="L16" s="14">
         <v>56</v>
       </c>
       <c r="M16" s="14">
-        <v>-22</v>
+        <v>-29.090909090909</v>
       </c>
       <c r="N16" s="14">
-        <v>-77.714285714285</v>
+        <v>-79.792746113989</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-33.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>-37.5</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J17" s="15">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K17" s="14">
-        <v>25.423728813559</v>
+        <v>33.870967741935</v>
       </c>
       <c r="L17" s="14">
-        <v>34.545454545454</v>
+        <v>33.870967741935</v>
       </c>
       <c r="M17" s="14">
-        <v>68.181818181818</v>
+        <v>80.434782608695</v>
       </c>
       <c r="N17" s="14">
-        <v>12.121212121212</v>
+        <v>16.901408450704</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="14">
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I18" s="15">
         <v>12</v>
       </c>
       <c r="J18" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K18" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M18" s="14">
-        <v>-82.857142857142</v>
+        <v>-84.415584415584</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.939393939393</v>
+        <v>-94.258373205741</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H19" s="14">
-        <v>-37.931034482758</v>
+        <v>-34.375</v>
       </c>
       <c r="I19" s="15">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J19" s="15">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K19" s="14">
-        <v>-24.096385542168</v>
+        <v>-25</v>
       </c>
       <c r="L19" s="14">
-        <v>-36.363636363636</v>
+        <v>-33.653846153846</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>4.545454545454</v>
       </c>
       <c r="N19" s="14">
-        <v>-41.121495327102</v>
+        <v>-39.473684210526</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>300</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
         <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>166.666666666667</v>
+        <v>60</v>
       </c>
       <c r="I20" s="15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J20" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K20" s="14">
-        <v>42.857142857142</v>
+        <v>36.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="M20" s="14">
-        <v>29.032258064516</v>
+        <v>13.888888888888</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.047619047619</v>
+        <v>-94.217207334273</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.254237288135</v>
+        <v>-9.375</v>
       </c>
       <c r="I21" s="17">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="J21" s="17">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="K21" s="18">
-        <v>6.392694063926</v>
+        <v>4.602510460251</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.271186440677</v>
+        <v>-1.574803149606</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.384615384615</v>
+        <v>-11.347517730496</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.026058631921</v>
+        <v>-80.857580398162</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,7 +1207,7 @@
         <v>100</v>
       </c>
       <c r="L22" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M22" s="14">
         <v>-50</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
+        <v>2</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="15">
         <v>3</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F23" s="15">
-        <v>2</v>
       </c>
       <c r="G23" s="15">
         <v>8</v>
       </c>
       <c r="H23" s="14">
-        <v>-75</v>
+        <v>-62.5</v>
       </c>
       <c r="I23" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J23" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K23" s="14">
-        <v>-20.588235294117</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L23" s="14">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="M23" s="14">
-        <v>125</v>
+        <v>115.384615384615</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="14">
-        <v>216.666666666667</v>
+        <v>140</v>
       </c>
       <c r="F24" s="15">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G24" s="15">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="H24" s="14">
-        <v>83.720930232558</v>
+        <v>143.75</v>
       </c>
       <c r="I24" s="15">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="J24" s="15">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K24" s="14">
-        <v>22.699386503067</v>
+        <v>26.190476190476</v>
       </c>
       <c r="L24" s="14">
-        <v>31.578947368421</v>
+        <v>30.864197530864</v>
       </c>
       <c r="M24" s="14">
-        <v>50.375939849624</v>
+        <v>49.295774647887</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15">
+        <v>12</v>
+      </c>
+      <c r="G25" s="15">
+        <v>8</v>
+      </c>
+      <c r="H25" s="14">
         <v>50</v>
       </c>
-      <c r="F25" s="15">
-        <v>13</v>
-      </c>
-      <c r="G25" s="15">
-        <v>10</v>
-      </c>
-      <c r="H25" s="14">
-        <v>30</v>
-      </c>
       <c r="I25" s="15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J25" s="15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K25" s="14">
         <v>0</v>
       </c>
       <c r="L25" s="14">
-        <v>21.212121212121</v>
+        <v>24.242424242424</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="F26" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I26" s="15">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J26" s="15">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="K26" s="14">
-        <v>8</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L26" s="14">
-        <v>16.129032258064</v>
+        <v>10.576923076923</v>
       </c>
       <c r="M26" s="14">
-        <v>-8.474576271186</v>
+        <v>-8</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,16 +1403,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="15">
         <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="L27" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
         <v>15</v>
       </c>
       <c r="J28" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="14">
+        <v>25</v>
+      </c>
+      <c r="L28" s="14">
         <v>36.363636363636</v>
-      </c>
-      <c r="L28" s="14">
-        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="15">
-        <v>2</v>
-      </c>
-      <c r="H29" s="14">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="15">
         <v>4</v>
@@ -1494,13 +1494,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L29" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M29" s="14">
         <v>-20</v>
       </c>
       <c r="N29" s="14">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="15">
-        <v>2</v>
-      </c>
-      <c r="H30" s="14">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="15">
         <v>1</v>
@@ -1535,13 +1535,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L30" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M30" s="14">
         <v>-75</v>
       </c>
       <c r="N30" s="14">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -881,8 +881,8 @@
       <c r="L14" s="14">
         <v>-100</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="14">
+        <v>-100</v>
       </c>
       <c r="N14" s="14">
         <v>-100</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,72 +902,72 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="15">
         <v>6</v>
       </c>
       <c r="K15" s="14">
+        <v>33.333333333333</v>
+      </c>
+      <c r="L15" s="14">
+        <v>166.666666666667</v>
+      </c>
+      <c r="M15" s="14">
+        <v>166.666666666667</v>
+      </c>
+      <c r="N15" s="14">
         <v>0</v>
-      </c>
-      <c r="L15" s="14">
-        <v>100</v>
-      </c>
-      <c r="M15" s="14">
-        <v>200</v>
-      </c>
-      <c r="N15" s="14">
-        <v>-14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F16" s="15">
+        <v>8</v>
+      </c>
+      <c r="G16" s="15">
         <v>7</v>
       </c>
-      <c r="G16" s="15">
-        <v>9</v>
-      </c>
       <c r="H16" s="14">
-        <v>-22.222222222222</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I16" s="15">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J16" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K16" s="14">
-        <v>5.405405405405</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L16" s="14">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="M16" s="14">
-        <v>-29.090909090909</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="N16" s="14">
-        <v>-79.792746113989</v>
+        <v>-79.611650485436</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>166.666666666667</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
-        <v>13.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J17" s="15">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K17" s="14">
-        <v>33.870967741935</v>
+        <v>30.882352941176</v>
       </c>
       <c r="L17" s="14">
-        <v>33.870967741935</v>
+        <v>30.882352941176</v>
       </c>
       <c r="M17" s="14">
-        <v>80.434782608695</v>
+        <v>67.924528301886</v>
       </c>
       <c r="N17" s="14">
-        <v>16.901408450704</v>
+        <v>12.658227848101</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-100</v>
+      <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
         <v>2</v>
       </c>
       <c r="H18" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="15">
         <v>12</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-7.692307692307</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-84.415584415584</v>
+        <v>-83.75</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.258373205741</v>
+        <v>-94.036697247706</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>8</v>
+      </c>
+      <c r="D19" s="15">
         <v>6</v>
       </c>
-      <c r="D19" s="15">
-        <v>9</v>
-      </c>
       <c r="E19" s="14">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G19" s="15">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>-34.375</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I19" s="15">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J19" s="15">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K19" s="14">
-        <v>-25</v>
+        <v>-19.387755102040</v>
       </c>
       <c r="L19" s="14">
-        <v>-33.653846153846</v>
+        <v>-30.088495575221</v>
       </c>
       <c r="M19" s="14">
-        <v>4.545454545454</v>
+        <v>8.219178082191</v>
       </c>
       <c r="N19" s="14">
-        <v>-39.473684210526</v>
+        <v>-35.772357723577</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>4</v>
+      </c>
+      <c r="D20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>300</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>60</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I20" s="15">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J20" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" s="14">
-        <v>36.666666666666</v>
+        <v>45.161290322580</v>
       </c>
       <c r="L20" s="14">
-        <v>-8.888888888888</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="M20" s="14">
-        <v>13.888888888888</v>
+        <v>25</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.217207334273</v>
+        <v>-93.991989319092</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F21" s="17">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.375</v>
+        <v>18.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="J21" s="17">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="K21" s="18">
-        <v>4.602510460251</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.574803149606</v>
+        <v>1.098901098901</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.347517730496</v>
+        <v>-9.508196721311</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.857580398162</v>
+        <v>-80.086580086580</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="15">
         <v>1</v>
       </c>
       <c r="K22" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L22" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="15">
         <v>3</v>
       </c>
       <c r="G23" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="14">
-        <v>-62.5</v>
+        <v>-70</v>
       </c>
       <c r="I23" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J23" s="15">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K23" s="14">
-        <v>-22.222222222222</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="L23" s="14">
-        <v>-20</v>
+        <v>-27.5</v>
       </c>
       <c r="M23" s="14">
-        <v>115.384615384615</v>
+        <v>81.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
+        <v>11</v>
+      </c>
+      <c r="D24" s="15">
         <v>12</v>
       </c>
-      <c r="D24" s="15">
-        <v>5</v>
-      </c>
       <c r="E24" s="14">
-        <v>140</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="G24" s="15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H24" s="14">
-        <v>143.75</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I24" s="15">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="J24" s="15">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="K24" s="14">
-        <v>26.190476190476</v>
+        <v>22.777777777777</v>
       </c>
       <c r="L24" s="14">
-        <v>30.864197530864</v>
+        <v>25.568181818181</v>
       </c>
       <c r="M24" s="14">
-        <v>49.295774647887</v>
+        <v>41.666666666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
         <v>1</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="15">
         <v>8</v>
       </c>
       <c r="H25" s="14">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="I25" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J25" s="15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K25" s="14">
-        <v>0</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L25" s="14">
-        <v>24.242424242424</v>
+        <v>27.777777777777</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="F26" s="15">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G26" s="15">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>13.043478260869</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="J26" s="15">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K26" s="14">
-        <v>9.523809523809</v>
+        <v>14.678899082568</v>
       </c>
       <c r="L26" s="14">
-        <v>10.576923076923</v>
+        <v>14.678899082568</v>
       </c>
       <c r="M26" s="14">
-        <v>-8</v>
+        <v>-8.759124087591</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" s="15">
         <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="L27" s="14">
-        <v>133.333333333333</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>3</v>
+      </c>
+      <c r="G28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15">
-        <v>2</v>
-      </c>
-      <c r="G28" s="15">
-        <v>2</v>
-      </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I28" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="15">
         <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>36.363636363636</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>-20</v>
       </c>
       <c r="M29" s="14">
-        <v>-20</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N29" s="14">
         <v>-60</v>
@@ -1538,7 +1538,7 @@
         <v>-80</v>
       </c>
       <c r="M30" s="14">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="14">
         <v>-88.888888888888</v>

--- a/data/source/weekly/cs-en-us-069pct.xlsx
+++ b/data/source/weekly/cs-en-us-069pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>3</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>200</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
         <v>8</v>
@@ -933,23 +933,23 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>3</v>
-      </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>200</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
         <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>14.285714285714</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I16" s="15">
         <v>42</v>
@@ -961,13 +961,13 @@
         <v>10.526315789473</v>
       </c>
       <c r="L16" s="14">
-        <v>68</v>
+        <v>61.538461538461</v>
       </c>
       <c r="M16" s="14">
-        <v>-26.315789473684</v>
+        <v>-31.147540983606</v>
       </c>
       <c r="N16" s="14">
-        <v>-79.611650485436</v>
+        <v>-80.821917808219</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F17" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>16.666666666666</v>
+        <v>36.842105263157</v>
       </c>
       <c r="I17" s="15">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="J17" s="15">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K17" s="14">
-        <v>30.882352941176</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>30.882352941176</v>
+        <v>31.506849315068</v>
       </c>
       <c r="M17" s="14">
-        <v>67.924528301886</v>
+        <v>68.421052631578</v>
       </c>
       <c r="N17" s="14">
-        <v>12.658227848101</v>
+        <v>15.662650602409</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="14">
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
         <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" s="14">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
         <v>-13.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-83.75</v>
+        <v>-84.523809523809</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.036697247706</v>
+        <v>-94.196428571428</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="F19" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G19" s="15">
         <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>-3.846153846153</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I19" s="15">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J19" s="15">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K19" s="14">
-        <v>-19.387755102040</v>
+        <v>-20.388349514563</v>
       </c>
       <c r="L19" s="14">
-        <v>-30.088495575221</v>
+        <v>-28.070175438596</v>
       </c>
       <c r="M19" s="14">
-        <v>8.219178082191</v>
+        <v>6.493506493506</v>
       </c>
       <c r="N19" s="14">
-        <v>-35.772357723577</v>
+        <v>-34.920634920634</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>300</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I20" s="15">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J20" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K20" s="14">
-        <v>45.161290322580</v>
+        <v>47.058823529411</v>
       </c>
       <c r="L20" s="14">
-        <v>-4.255319148936</v>
+        <v>0</v>
       </c>
       <c r="M20" s="14">
-        <v>25</v>
+        <v>31.578947368421</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.991989319092</v>
+        <v>-93.589743589743</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>71.428571428571</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H21" s="18">
-        <v>18.333333333333</v>
+        <v>12.903225806451</v>
       </c>
       <c r="I21" s="17">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="J21" s="17">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="K21" s="18">
-        <v>9.090909090909</v>
+        <v>9.398496240601</v>
       </c>
       <c r="L21" s="18">
-        <v>1.098901098901</v>
+        <v>2.826855123674</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.508196721311</v>
+        <v>-9.907120743034</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.086580086580</v>
+        <v>-79.833679833679</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
+        <v>3</v>
+      </c>
+      <c r="D23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="15">
-        <v>3</v>
-      </c>
       <c r="E23" s="14">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="F23" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G23" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H23" s="14">
-        <v>-70</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J23" s="15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23" s="14">
-        <v>-25.641025641025</v>
+        <v>-20</v>
       </c>
       <c r="L23" s="14">
-        <v>-27.5</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="M23" s="14">
-        <v>81.25</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E24" s="14">
-        <v>-8.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G24" s="15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H24" s="14">
-        <v>83.333333333333</v>
+        <v>78.125</v>
       </c>
       <c r="I24" s="15">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="J24" s="15">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="K24" s="14">
-        <v>22.777777777777</v>
+        <v>24.867724867724</v>
       </c>
       <c r="L24" s="14">
-        <v>25.568181818181</v>
+        <v>28.260869565217</v>
       </c>
       <c r="M24" s="14">
-        <v>41.666666666666</v>
+        <v>41.317365269461</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>5</v>
+      </c>
+      <c r="D25" s="15">
         <v>2</v>
       </c>
-      <c r="D25" s="15">
-        <v>1</v>
-      </c>
       <c r="E25" s="14">
+        <v>150</v>
+      </c>
+      <c r="F25" s="15">
+        <v>12</v>
+      </c>
+      <c r="G25" s="15">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
         <v>100</v>
       </c>
-      <c r="F25" s="15">
-        <v>11</v>
-      </c>
-      <c r="G25" s="15">
-        <v>8</v>
-      </c>
-      <c r="H25" s="14">
-        <v>37.5</v>
-      </c>
       <c r="I25" s="15">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J25" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K25" s="14">
-        <v>9.523809523809</v>
+        <v>15.909090909090</v>
       </c>
       <c r="L25" s="14">
-        <v>27.777777777777</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
         <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H26" s="14">
-        <v>83.333333333333</v>
+        <v>93.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J26" s="15">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K26" s="14">
-        <v>14.678899082568</v>
+        <v>15.929203539823</v>
       </c>
       <c r="L26" s="14">
-        <v>14.678899082568</v>
+        <v>16.964285714285</v>
       </c>
       <c r="M26" s="14">
-        <v>-8.759124087591</v>
+        <v>-10.273972602739</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>3</v>
-      </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>200</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
         <v>9</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
+        <v>2</v>
+      </c>
+      <c r="G28" s="15">
         <v>3</v>
       </c>
-      <c r="G28" s="15">
-        <v>1</v>
-      </c>
       <c r="H28" s="14">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
         <v>16</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="14">
         <v>33.333333333333</v>
